--- a/data/trans_camb/P12_1_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P12_1_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,33; -0,04</t>
+          <t>-7,5; -0,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 0,27</t>
+          <t>-7,02; 0,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,49; -0,49</t>
+          <t>-8,6; -0,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 9,15</t>
+          <t>2,01; 8,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 2,74</t>
+          <t>-4,77; 2,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 3,32</t>
+          <t>-3,51; 3,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 4,15</t>
+          <t>-0,97; 4,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 0,75</t>
+          <t>-4,56; 0,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 1,08</t>
+          <t>-4,21; 0,95</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,01; -0,0</t>
+          <t>-30,4; -1,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,38; 1,34</t>
+          <t>-29,19; 3,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,96; -1,88</t>
+          <t>-35,98; -2,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,39; 37,01</t>
+          <t>7,0; 36,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 11,0</t>
+          <t>-17,45; 11,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 13,78</t>
+          <t>-12,43; 13,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 18,15</t>
+          <t>-3,8; 17,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,13; 3,35</t>
+          <t>-17,92; 2,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 4,63</t>
+          <t>-16,49; 4,06</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 3,13</t>
+          <t>-1,62; 3,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,79; -2,29</t>
+          <t>-6,82; -2,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,9; -0,52</t>
+          <t>-6,99; -0,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,68</t>
+          <t>0,73; 6,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,43; -4,36</t>
+          <t>-9,49; -4,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 26,57</t>
+          <t>-4,41; 23,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,03</t>
+          <t>0,37; 4,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,62; -4,08</t>
+          <t>-7,48; -4,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 13,88</t>
+          <t>-4,06; 13,36</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 24,48</t>
+          <t>-10,55; 24,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-44,17; -17,79</t>
+          <t>-43,75; -18,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-44,98; -4,11</t>
+          <t>-46,48; -3,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 34,96</t>
+          <t>3,39; 36,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,66; -23,39</t>
+          <t>-43,94; -23,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 133,19</t>
+          <t>-21,52; 118,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 25,09</t>
+          <t>2,12; 25,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,94; -25,57</t>
+          <t>-41,41; -25,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,14; 85,75</t>
+          <t>-23,12; 79,54</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 3,2</t>
+          <t>-5,86; 2,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,8; -1,2</t>
+          <t>-9,6; -1,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 2,59</t>
+          <t>-6,11; 2,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 2,52</t>
+          <t>-8,08; 1,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,03; -0,75</t>
+          <t>-10,27; -0,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 2,61</t>
+          <t>-6,66; 2,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 1,38</t>
+          <t>-5,43; 1,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,92; -2,38</t>
+          <t>-8,53; -2,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 1,28</t>
+          <t>-4,7; 1,47</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,68; 26,66</t>
+          <t>-35,43; 22,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-56,87; -8,57</t>
+          <t>-56,03; -12,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-33,68; 21,62</t>
+          <t>-36,65; 19,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,64; 16,05</t>
+          <t>-36,58; 12,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-45,42; -4,1</t>
+          <t>-46,76; -4,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,07; 16,5</t>
+          <t>-29,64; 15,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-31,39; 8,91</t>
+          <t>-29,23; 8,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,21; -15,07</t>
+          <t>-45,51; -14,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 8,66</t>
+          <t>-24,66; 9,67</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 0,64</t>
+          <t>-3,03; 0,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -3,47</t>
+          <t>-7,2; -3,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,01; -2,31</t>
+          <t>-7,28; -2,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,63</t>
+          <t>1,43; 5,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,71; -3,81</t>
+          <t>-7,64; -3,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 17,5</t>
+          <t>-4,13; 14,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,58</t>
+          <t>-0,19; 2,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,75; -4,13</t>
+          <t>-6,76; -4,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 8,37</t>
+          <t>-4,68; 7,44</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 4,03</t>
+          <t>-16,96; 3,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-38,87; -21,31</t>
+          <t>-40,0; -22,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,61; -14,2</t>
+          <t>-42,21; -14,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,21; 26,47</t>
+          <t>5,92; 26,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,61; -17,8</t>
+          <t>-32,89; -17,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 79,49</t>
+          <t>-18,25; 66,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 13,57</t>
+          <t>-0,94; 13,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-33,1; -21,59</t>
+          <t>-33,17; -22,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-22,0; 45,86</t>
+          <t>-23,52; 38,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P12_1_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P12_1_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-4,7</t>
+          <t>-5,53</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,75</t>
+          <t>-2,04</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,5; -0,38</t>
+          <t>-7,6; -0,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 0,7</t>
+          <t>-6,95; 0,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,6; -0,54</t>
+          <t>-9,19; -1,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 8,88</t>
+          <t>1,88; 8,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 2,89</t>
+          <t>-4,42; 2,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 3,38</t>
+          <t>-3,35; 3,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 4,12</t>
+          <t>-0,85; 4,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 0,49</t>
+          <t>-4,64; 0,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 0,95</t>
+          <t>-4,46; 0,66</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-20,82%</t>
+          <t>-24,47%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-7,13%</t>
+          <t>-8,3%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,4; -1,14</t>
+          <t>-30,73; -0,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,19; 3,42</t>
+          <t>-29,22; 0,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-35,98; -2,62</t>
+          <t>-37,98; -4,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 36,21</t>
+          <t>6,89; 36,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 11,67</t>
+          <t>-16,07; 11,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 13,7</t>
+          <t>-12,23; 14,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 17,55</t>
+          <t>-3,43; 17,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 2,12</t>
+          <t>-18,05; 3,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 4,06</t>
+          <t>-17,56; 2,89</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,96</t>
+          <t>-1,8</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,15</t>
+          <t>-2,67</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>-2,18</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 3,19</t>
+          <t>-1,78; 3,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,82; -2,48</t>
+          <t>-6,75; -2,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,99; -0,47</t>
+          <t>-4,04; 0,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,77</t>
+          <t>1,01; 6,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,49; -4,44</t>
+          <t>-9,51; -4,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 23,58</t>
+          <t>-5,22; -0,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,02</t>
+          <t>0,35; 4,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,48; -4,06</t>
+          <t>-7,26; -3,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 13,36</t>
+          <t>-3,97; -0,59</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-20,88%</t>
+          <t>-12,71%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>-13,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>-12,72%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 24,55</t>
+          <t>-11,43; 24,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-43,75; -18,88</t>
+          <t>-44,61; -19,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,48; -3,48</t>
+          <t>-26,23; 4,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 36,66</t>
+          <t>4,8; 35,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,94; -23,99</t>
+          <t>-43,58; -23,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,52; 118,25</t>
+          <t>-23,55; 0,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 25,37</t>
+          <t>2,3; 26,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,41; -25,21</t>
+          <t>-40,16; -24,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,12; 79,54</t>
+          <t>-21,77; -3,52</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,66</t>
+          <t>-1,27</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,81</t>
+          <t>-1,63</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,54</t>
+          <t>-1,26</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 2,98</t>
+          <t>-6,12; 3,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,6; -1,48</t>
+          <t>-9,51; -1,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 2,42</t>
+          <t>-5,58; 2,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 1,95</t>
+          <t>-7,53; 2,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,27; -0,71</t>
+          <t>-10,32; -0,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 2,5</t>
+          <t>-6,24; 2,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 1,31</t>
+          <t>-5,71; 1,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,53; -2,25</t>
+          <t>-8,41; -2,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 1,47</t>
+          <t>-4,42; 1,82</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-11,2%</t>
+          <t>-8,62%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-9,38%</t>
+          <t>-8,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-9,17%</t>
+          <t>-7,47%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-35,43; 22,58</t>
+          <t>-36,56; 22,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-56,03; -12,44</t>
+          <t>-56,62; -13,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,65; 19,79</t>
+          <t>-32,4; 20,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-36,58; 12,24</t>
+          <t>-34,85; 17,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,76; -4,21</t>
+          <t>-47,42; -4,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,64; 15,0</t>
+          <t>-27,66; 15,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,23; 8,66</t>
+          <t>-30,06; 9,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-45,51; -14,92</t>
+          <t>-45,81; -14,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 9,67</t>
+          <t>-23,43; 11,68</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-4,36</t>
+          <t>-3,55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,11</t>
+          <t>-2,87</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,51</t>
+          <t>-3,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,53</t>
+          <t>-2,91; 0,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,2; -3,76</t>
+          <t>-6,97; -3,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,28; -2,38</t>
+          <t>-5,31; -1,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,71</t>
+          <t>1,39; 5,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,64; -3,84</t>
+          <t>-7,6; -3,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 14,88</t>
+          <t>-4,69; -1,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 2,53</t>
+          <t>-0,14; 2,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,76; -4,23</t>
+          <t>-6,72; -4,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 7,44</t>
+          <t>-4,4; -1,96</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-25,74%</t>
+          <t>-20,99%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>-12,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-7,67%</t>
+          <t>-16,08%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 3,29</t>
+          <t>-16,26; 4,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-40,0; -22,94</t>
+          <t>-38,92; -22,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,21; -14,85</t>
+          <t>-29,7; -10,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,92; 26,59</t>
+          <t>6,02; 26,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,89; -17,9</t>
+          <t>-32,48; -17,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 66,49</t>
+          <t>-19,93; -4,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 13,44</t>
+          <t>-0,7; 13,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-33,17; -22,49</t>
+          <t>-33,17; -21,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 38,3</t>
+          <t>-21,67; -10,51</t>
         </is>
       </c>
     </row>
